--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-encounter.xlsx
@@ -369,7 +369,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -741,7 +741,7 @@
     <t>受療行動のタイプ。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-type|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -765,7 +765,7 @@
     <t>提供されるサービスの広範な分類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -827,7 +827,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -853,7 +853,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -908,7 +908,7 @@
     <t>参加者タイプは、個人がどのようにエンカウントに参加するかを示します。それには、非開業者の参加者が含まれ、開業者にとってはこのエンカウントの文脈でアクションタイプを説明することが含まれます（例：入院医師、診療医師、翻訳者、相談医師）。これは、雇用、教育、免許などの用語から派生した機能的な役割である開業者の役割とは異なります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -963,7 +963,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment)
+    <t xml:space="preserve">Reference(Appointment|4.0.1)
 </t>
   </si>
   <si>
@@ -1044,7 +1044,7 @@
     <t>受療行動が起こる理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1128,7 +1128,7 @@
     <t>この状態が表す診断のタイプ。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1150,7 +1150,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1225,7 +1225,7 @@
     <t>患者がどこから入院したのか（医師の紹介、転院）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1270,7 +1270,7 @@
     <t>食品の好みを考慮して、医療、文化、倫理的観点から、提供要件に対応することができます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1291,7 +1291,7 @@
     <t>特別なおもてなし。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1312,7 +1312,7 @@
     <t>特別な手配。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1345,7 +1345,7 @@
     <t>退院後の場所のカテゴリーまたは種類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.0.1</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1437,7 +1437,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1816,7 +1816,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="40.51171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
